--- a/9983.T.xlsx
+++ b/9983.T.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC86DA6-461B-4677-9A23-9B5C0CF81F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52065E59-777B-4C5B-9B20-74D44B8E1BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{C51DE7BF-0E76-4BFC-AC60-72AAABFBEE4E}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{C51DE7BF-0E76-4BFC-AC60-72AAABFBEE4E}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -280,13 +280,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -480,37 +486,40 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -879,7 +888,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="3">
-        <v>62750</v>
+        <v>75540</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -890,10 +899,10 @@
         <v>2</v>
       </c>
       <c r="J4" s="3">
-        <v>306.82456000000002</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>74</v>
+        <v>306.82905399999999</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -905,7 +914,7 @@
       </c>
       <c r="J5" s="3">
         <f>J4*J3</f>
-        <v>19253241.140000001</v>
+        <v>23177866.739159998</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -913,11 +922,10 @@
         <v>4</v>
       </c>
       <c r="J6" s="3">
-        <f>923697+1059881</f>
-        <v>1983578</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>74</v>
+        <v>1040505</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -935,11 +943,11 @@
         <v>5</v>
       </c>
       <c r="J7" s="3">
-        <f>174468+140975</f>
-        <v>315443</v>
-      </c>
-      <c r="K7" s="24" t="s">
-        <v>74</v>
+        <f>113856+141500</f>
+        <v>255356</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -954,7 +962,7 @@
       </c>
       <c r="J8" s="3">
         <f>J5+J7-J6</f>
-        <v>17585106.140000001</v>
+        <v>22392717.739159998</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -1016,8 +1024,8 @@
     <col min="1" max="1" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" style="2" customWidth="1"/>
     <col min="3" max="10" width="9.140625" style="2"/>
-    <col min="11" max="11" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="18" width="9.140625" style="2"/>
+    <col min="11" max="12" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="9.140625" style="2"/>
     <col min="19" max="20" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="9.140625" style="2"/>
   </cols>
@@ -1115,7 +1123,9 @@
       <c r="K3" s="3">
         <v>299069</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="3">
+        <v>282671</v>
+      </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -1191,7 +1201,9 @@
       <c r="K4" s="3">
         <v>191161</v>
       </c>
-      <c r="L4" s="3"/>
+      <c r="L4" s="3">
+        <v>196612</v>
+      </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -1267,7 +1279,9 @@
       <c r="K5" s="3">
         <v>187051</v>
       </c>
-      <c r="L5" s="3"/>
+      <c r="L5" s="3">
+        <v>222010</v>
+      </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -1343,7 +1357,9 @@
       <c r="K6" s="3">
         <v>88695</v>
       </c>
-      <c r="L6" s="3"/>
+      <c r="L6" s="3">
+        <v>88875</v>
+      </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -1419,7 +1435,9 @@
       <c r="K7" s="3">
         <v>136954</v>
       </c>
-      <c r="L7" s="3"/>
+      <c r="L7" s="3">
+        <v>130017</v>
+      </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
@@ -1495,7 +1513,9 @@
       <c r="K8" s="3">
         <v>299069</v>
       </c>
-      <c r="L8" s="3"/>
+      <c r="L8" s="3">
+        <v>282671</v>
+      </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -1580,7 +1600,9 @@
       <c r="K9" s="3">
         <v>603863</v>
       </c>
-      <c r="L9" s="3"/>
+      <c r="L9" s="3">
+        <v>637514</v>
+      </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -1665,7 +1687,9 @@
       <c r="K10" s="3">
         <v>91366</v>
       </c>
-      <c r="L10" s="3"/>
+      <c r="L10" s="3">
+        <v>77110</v>
+      </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
@@ -1750,7 +1774,9 @@
       <c r="K11" s="3">
         <v>33077</v>
       </c>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3">
+        <v>29635</v>
+      </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
@@ -1835,7 +1861,9 @@
       <c r="K12" s="3">
         <v>368</v>
       </c>
-      <c r="L12" s="3"/>
+      <c r="L12" s="3">
+        <v>552</v>
+      </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
@@ -1921,7 +1949,9 @@
       <c r="K13" s="19">
         <v>1027745</v>
       </c>
-      <c r="L13" s="19"/>
+      <c r="L13" s="19">
+        <v>1027482</v>
+      </c>
       <c r="M13" s="19"/>
       <c r="N13" s="19"/>
       <c r="O13" s="3"/>
@@ -2006,7 +2036,9 @@
       <c r="K14" s="3">
         <v>460042</v>
       </c>
-      <c r="L14" s="3"/>
+      <c r="L14" s="3">
+        <v>483611</v>
+      </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
@@ -2061,7 +2093,7 @@
         <v>21</v>
       </c>
       <c r="C15" s="3">
-        <f t="shared" ref="C15:K15" si="2">+C13-C14</f>
+        <f t="shared" ref="C15:L15" si="2">+C13-C14</f>
         <v>442823</v>
       </c>
       <c r="D15" s="3">
@@ -2096,7 +2128,9 @@
         <f t="shared" si="2"/>
         <v>567703</v>
       </c>
-      <c r="L15" s="3"/>
+      <c r="L15" s="3">
+        <v>543871</v>
+      </c>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
@@ -2192,7 +2226,9 @@
       <c r="K16" s="3">
         <v>362055</v>
       </c>
-      <c r="L16" s="3"/>
+      <c r="L16" s="3">
+        <v>362555</v>
+      </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -2277,7 +2313,9 @@
       <c r="K17" s="3">
         <v>5360</v>
       </c>
-      <c r="L17" s="3"/>
+      <c r="L17" s="3">
+        <v>9940</v>
+      </c>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
@@ -2362,7 +2400,9 @@
       <c r="K18" s="3">
         <v>1030</v>
       </c>
-      <c r="L18" s="3"/>
+      <c r="L18" s="3">
+        <v>1801</v>
+      </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
@@ -2447,7 +2487,9 @@
       <c r="K19" s="3">
         <v>937</v>
       </c>
-      <c r="L19" s="3"/>
+      <c r="L19" s="3">
+        <v>297</v>
+      </c>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
@@ -2502,7 +2544,7 @@
         <v>26</v>
       </c>
       <c r="C20" s="3">
-        <f t="shared" ref="C20:K20" si="4">+C15-C16+C17-C18+C19</f>
+        <f t="shared" ref="C20:L20" si="4">+C15-C16+C17-C18+C19</f>
         <v>146688</v>
       </c>
       <c r="D20" s="3">
@@ -2537,7 +2579,9 @@
         <f t="shared" si="4"/>
         <v>210915</v>
       </c>
-      <c r="L20" s="3"/>
+      <c r="L20" s="3">
+        <v>189752</v>
+      </c>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
@@ -2633,7 +2677,9 @@
       <c r="K21" s="3">
         <v>19387</v>
       </c>
-      <c r="L21" s="3"/>
+      <c r="L21" s="3">
+        <v>15832</v>
+      </c>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
@@ -2718,7 +2764,9 @@
       <c r="K22" s="3">
         <v>3634</v>
       </c>
-      <c r="L22" s="3"/>
+      <c r="L22" s="3">
+        <v>3447</v>
+      </c>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
@@ -2773,7 +2821,7 @@
         <v>29</v>
       </c>
       <c r="C23" s="3">
-        <f t="shared" ref="C23:K23" si="6">+C20+C21-C22</f>
+        <f t="shared" ref="C23:L23" si="6">+C20+C21-C22</f>
         <v>162473</v>
       </c>
       <c r="D23" s="3">
@@ -2808,7 +2856,9 @@
         <f t="shared" si="6"/>
         <v>226668</v>
       </c>
-      <c r="L23" s="3"/>
+      <c r="L23" s="3">
+        <v>202137</v>
+      </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -2903,7 +2953,9 @@
       <c r="K24" s="3">
         <v>68153</v>
       </c>
-      <c r="L24" s="3"/>
+      <c r="L24" s="3">
+        <v>58508</v>
+      </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
@@ -2958,7 +3010,7 @@
         <v>31</v>
       </c>
       <c r="C25" s="3">
-        <f t="shared" ref="C25:K25" si="8">+C23-C24</f>
+        <f t="shared" ref="C25:L25" si="8">+C23-C24</f>
         <v>114709</v>
       </c>
       <c r="D25" s="3">
@@ -2993,7 +3045,9 @@
         <f t="shared" si="8"/>
         <v>158515</v>
       </c>
-      <c r="L25" s="3"/>
+      <c r="L25" s="3">
+        <v>143629</v>
+      </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -3088,7 +3142,9 @@
       <c r="K26" s="3">
         <v>11067</v>
       </c>
-      <c r="L26" s="3"/>
+      <c r="L26" s="3">
+        <v>11785</v>
+      </c>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -3143,7 +3199,7 @@
         <v>33</v>
       </c>
       <c r="C27" s="3">
-        <f t="shared" ref="C27:K27" si="10">+C25-C26</f>
+        <f t="shared" ref="C27:L27" si="10">+C25-C26</f>
         <v>107804</v>
       </c>
       <c r="D27" s="3">
@@ -3178,7 +3234,9 @@
         <f t="shared" si="10"/>
         <v>147448</v>
       </c>
-      <c r="L27" s="3"/>
+      <c r="L27" s="3">
+        <v>131844</v>
+      </c>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -3335,7 +3393,10 @@
         <f t="shared" si="13"/>
         <v>480.56126928039919</v>
       </c>
-      <c r="L29" s="20"/>
+      <c r="L29" s="20">
+        <f t="shared" si="13"/>
+        <v>429.69855129820922</v>
+      </c>
       <c r="M29" s="20"/>
       <c r="N29" s="20"/>
       <c r="O29" s="3"/>
@@ -3429,7 +3490,9 @@
       <c r="K30" s="3">
         <v>306.82456000000002</v>
       </c>
-      <c r="L30" s="3"/>
+      <c r="L30" s="3">
+        <v>306.82905399999999</v>
+      </c>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
@@ -3556,14 +3619,17 @@
         <v>0.75231563552561598</v>
       </c>
       <c r="J32" s="21">
-        <f t="shared" ref="J32:K42" si="15">+J3/F3-1</f>
+        <f t="shared" ref="J32:L42" si="15">+J3/F3-1</f>
         <v>6.9010800780320736E-2</v>
       </c>
       <c r="K32" s="21">
         <f t="shared" si="15"/>
         <v>0.12178078183959617</v>
       </c>
-      <c r="L32" s="21"/>
+      <c r="L32" s="21">
+        <f t="shared" si="15"/>
+        <v>0.29365326352594434</v>
+      </c>
       <c r="M32" s="21"/>
       <c r="N32" s="21"/>
       <c r="O32" s="3"/>
@@ -3637,7 +3703,10 @@
         <f t="shared" si="15"/>
         <v>7.0270421588936705E-2</v>
       </c>
-      <c r="L33" s="21"/>
+      <c r="L33" s="21">
+        <f t="shared" si="15"/>
+        <v>8.121841368653171E-2</v>
+      </c>
       <c r="M33" s="21"/>
       <c r="N33" s="21"/>
       <c r="O33" s="3"/>
@@ -3711,7 +3780,10 @@
         <f t="shared" si="15"/>
         <v>0.21352943466244545</v>
       </c>
-      <c r="L34" s="21"/>
+      <c r="L34" s="21">
+        <f t="shared" si="15"/>
+        <v>0.87066059993259182</v>
+      </c>
       <c r="M34" s="21"/>
       <c r="N34" s="21"/>
       <c r="O34" s="3"/>
@@ -3785,7 +3857,10 @@
         <f t="shared" si="15"/>
         <v>0.30408892417626032</v>
       </c>
-      <c r="L35" s="21"/>
+      <c r="L35" s="21">
+        <f t="shared" si="15"/>
+        <v>1.192982456140351</v>
+      </c>
       <c r="M35" s="21"/>
       <c r="N35" s="21"/>
       <c r="O35" s="3"/>
@@ -3859,7 +3934,10 @@
         <f t="shared" si="15"/>
         <v>0.34263362221089366</v>
       </c>
-      <c r="L36" s="21"/>
+      <c r="L36" s="21">
+        <f t="shared" si="15"/>
+        <v>2.2368303126867159</v>
+      </c>
       <c r="M36" s="21"/>
       <c r="N36" s="21"/>
       <c r="O36" s="3"/>
@@ -3933,7 +4011,10 @@
         <f t="shared" si="15"/>
         <v>0.12178078183959617</v>
       </c>
-      <c r="L37" s="21"/>
+      <c r="L37" s="21">
+        <f t="shared" si="15"/>
+        <v>0.29365326352594434</v>
+      </c>
       <c r="M37" s="21"/>
       <c r="N37" s="21"/>
       <c r="O37" s="3"/>
@@ -4007,7 +4088,10 @@
         <f t="shared" si="15"/>
         <v>0.20347292667712313</v>
       </c>
-      <c r="L38" s="21"/>
+      <c r="L38" s="21">
+        <f t="shared" si="15"/>
+        <v>0.66793295972455513</v>
+      </c>
       <c r="M38" s="21"/>
       <c r="N38" s="21"/>
       <c r="O38" s="3"/>
@@ -4081,7 +4165,10 @@
         <f t="shared" si="15"/>
         <v>8.3434499503365345E-3</v>
       </c>
-      <c r="L39" s="21"/>
+      <c r="L39" s="21">
+        <f t="shared" si="15"/>
+        <v>0.11811959863116983</v>
+      </c>
       <c r="M39" s="21"/>
       <c r="N39" s="21"/>
       <c r="O39" s="3"/>
@@ -4155,7 +4242,10 @@
         <f t="shared" si="15"/>
         <v>-7.5906576521204694E-2</v>
       </c>
-      <c r="L40" s="21"/>
+      <c r="L40" s="21">
+        <f t="shared" si="15"/>
+        <v>-0.1186092853106504</v>
+      </c>
       <c r="M40" s="21"/>
       <c r="N40" s="21"/>
       <c r="O40" s="3"/>
@@ -4229,7 +4319,10 @@
         <f t="shared" si="15"/>
         <v>-0.11750599520383698</v>
       </c>
-      <c r="L41" s="21"/>
+      <c r="L41" s="21">
+        <f t="shared" si="15"/>
+        <v>0.11515151515151523</v>
+      </c>
       <c r="M41" s="21"/>
       <c r="N41" s="21"/>
       <c r="O41" s="3"/>
@@ -4303,7 +4396,10 @@
         <f t="shared" si="15"/>
         <v>0.14807214541684921</v>
       </c>
-      <c r="L42" s="22"/>
+      <c r="L42" s="22">
+        <f t="shared" si="15"/>
+        <v>0.14801688480300701</v>
+      </c>
       <c r="M42" s="22"/>
       <c r="N42" s="22"/>
       <c r="O42" s="3"/>
@@ -4389,7 +4485,10 @@
         <f t="shared" si="18"/>
         <v>0.5523772920325567</v>
       </c>
-      <c r="L43" s="21"/>
+      <c r="L43" s="21">
+        <f t="shared" ref="L43" si="19">+L15/L13</f>
+        <v>0.52932411468035445</v>
+      </c>
       <c r="M43" s="21"/>
       <c r="N43" s="21"/>
       <c r="O43" s="3"/>
@@ -4440,19 +4539,19 @@
         <v>62</v>
       </c>
       <c r="C44" s="21">
-        <f t="shared" ref="C44:F44" si="19">+C20/C13</f>
+        <f t="shared" ref="C44:F44" si="20">+C20/C13</f>
         <v>0.18091024908951658</v>
       </c>
       <c r="D44" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.14006694021310231</v>
       </c>
       <c r="E44" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.18856107215355791</v>
       </c>
       <c r="F44" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.13440159493310369</v>
       </c>
       <c r="G44" s="21">
@@ -4468,14 +4567,17 @@
         <v>0.17753566200045975</v>
       </c>
       <c r="J44" s="21">
-        <f t="shared" ref="J44:K44" si="20">+J20/J13</f>
+        <f t="shared" ref="J44:K44" si="21">+J20/J13</f>
         <v>0.14456304994316377</v>
       </c>
       <c r="K44" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.20522113948498899</v>
       </c>
-      <c r="L44" s="21"/>
+      <c r="L44" s="21">
+        <f t="shared" ref="L44" si="22">+L20/L13</f>
+        <v>0.18467671453125212</v>
+      </c>
       <c r="M44" s="21"/>
       <c r="N44" s="21"/>
       <c r="O44" s="3"/>
@@ -4526,19 +4628,19 @@
         <v>63</v>
       </c>
       <c r="C45" s="21">
-        <f t="shared" ref="C45:F45" si="21">+C24/C23</f>
+        <f t="shared" ref="C45:F45" si="23">+C24/C23</f>
         <v>0.29398115379170692</v>
       </c>
       <c r="D45" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.30815354727509092</v>
       </c>
       <c r="E45" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.31323511274064608</v>
       </c>
       <c r="F45" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.22366019160802186</v>
       </c>
       <c r="G45" s="21">
@@ -4554,14 +4656,17 @@
         <v>0.29631330526852917</v>
       </c>
       <c r="J45" s="21">
-        <f t="shared" ref="J45:K45" si="22">+J24/J23</f>
+        <f t="shared" ref="J45:K45" si="24">+J24/J23</f>
         <v>3.6849672097117682E-2</v>
       </c>
       <c r="K45" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.30067323133393331</v>
       </c>
-      <c r="L45" s="21"/>
+      <c r="L45" s="21">
+        <f t="shared" ref="L45" si="25">+L24/L23</f>
+        <v>0.28944725606890376</v>
+      </c>
       <c r="M45" s="21"/>
       <c r="N45" s="21"/>
       <c r="O45" s="3"/>

--- a/9983.T.xlsx
+++ b/9983.T.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52065E59-777B-4C5B-9B20-74D44B8E1BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E818962C-3E03-4FE1-81A7-6108584C9467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{C51DE7BF-0E76-4BFC-AC60-72AAABFBEE4E}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{C51DE7BF-0E76-4BFC-AC60-72AAABFBEE4E}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -888,7 +888,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="3">
-        <v>75540</v>
+        <v>82110</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -899,10 +899,10 @@
         <v>2</v>
       </c>
       <c r="J4" s="3">
-        <v>306.82905399999999</v>
+        <v>306.83511800000002</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -914,7 +914,7 @@
       </c>
       <c r="J5" s="3">
         <f>J4*J3</f>
-        <v>23177866.739159998</v>
+        <v>25194231.538980003</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -922,10 +922,10 @@
         <v>4</v>
       </c>
       <c r="J6" s="3">
-        <v>1040505</v>
+        <v>1132.078</v>
       </c>
       <c r="K6" s="25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -943,11 +943,11 @@
         <v>5</v>
       </c>
       <c r="J7" s="3">
-        <f>113856+141500</f>
-        <v>255356</v>
+        <f>91380+141535</f>
+        <v>232915</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -962,7 +962,7 @@
       </c>
       <c r="J8" s="3">
         <f>J5+J7-J6</f>
-        <v>22392717.739159998</v>
+        <v>25426014.460980002</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -1024,8 +1024,8 @@
     <col min="1" max="1" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" style="2" customWidth="1"/>
     <col min="3" max="10" width="9.140625" style="2"/>
-    <col min="11" max="12" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="9.140625" style="2"/>
+    <col min="11" max="13" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="9.140625" style="2"/>
     <col min="19" max="20" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="9.140625" style="2"/>
   </cols>
@@ -1126,7 +1126,10 @@
       <c r="L3" s="3">
         <v>282671</v>
       </c>
-      <c r="M3" s="3"/>
+      <c r="M3" s="3">
+        <f>867690-SUM(K3:L3)</f>
+        <v>285950</v>
+      </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
@@ -1204,7 +1207,10 @@
       <c r="L4" s="3">
         <v>196612</v>
       </c>
-      <c r="M4" s="3"/>
+      <c r="M4" s="3">
+        <f>560839-SUM(K4:L4)</f>
+        <v>173066</v>
+      </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
@@ -1282,7 +1288,10 @@
       <c r="L5" s="3">
         <v>222010</v>
       </c>
-      <c r="M5" s="3"/>
+      <c r="M5" s="3">
+        <f>617575-SUM(K5:L5)</f>
+        <v>208514</v>
+      </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
@@ -1360,7 +1369,10 @@
       <c r="L6" s="3">
         <v>88875</v>
       </c>
-      <c r="M6" s="3"/>
+      <c r="M6" s="3">
+        <f>268164-SUM(K6:L6)</f>
+        <v>90594</v>
+      </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
@@ -1438,7 +1450,10 @@
       <c r="L7" s="3">
         <v>130017</v>
       </c>
-      <c r="M7" s="3"/>
+      <c r="M7" s="3">
+        <f>387447-SUM(K7:L7)</f>
+        <v>120476</v>
+      </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -1516,7 +1531,10 @@
       <c r="L8" s="3">
         <v>282671</v>
       </c>
-      <c r="M8" s="3"/>
+      <c r="M8" s="3">
+        <f>867690-SUM(K8:L8)</f>
+        <v>285950</v>
+      </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
@@ -1603,7 +1621,10 @@
       <c r="L9" s="3">
         <v>637514</v>
       </c>
-      <c r="M9" s="3"/>
+      <c r="M9" s="3">
+        <f>1834026-SUM(K9:L9)</f>
+        <v>592649</v>
+      </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -1690,7 +1711,10 @@
       <c r="L10" s="3">
         <v>77110</v>
       </c>
-      <c r="M10" s="3"/>
+      <c r="M10" s="3">
+        <f>265668-SUM(K10:L10)</f>
+        <v>97192</v>
+      </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1777,7 +1801,10 @@
       <c r="L11" s="3">
         <v>29635</v>
       </c>
-      <c r="M11" s="3"/>
+      <c r="M11" s="3">
+        <f>96313-SUM(K11:L11)</f>
+        <v>33601</v>
+      </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1864,7 +1891,10 @@
       <c r="L12" s="3">
         <v>552</v>
       </c>
-      <c r="M12" s="3"/>
+      <c r="M12" s="3">
+        <f>1483-SUM(K12:L12)</f>
+        <v>563</v>
+      </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1952,7 +1982,10 @@
       <c r="L13" s="19">
         <v>1027482</v>
       </c>
-      <c r="M13" s="19"/>
+      <c r="M13" s="19">
+        <f>3065182-SUM(K13:L13)</f>
+        <v>1009955</v>
+      </c>
       <c r="N13" s="19"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -2039,7 +2072,10 @@
       <c r="L14" s="3">
         <v>483611</v>
       </c>
-      <c r="M14" s="3"/>
+      <c r="M14" s="3">
+        <f>1381571-SUM(K14:L14)</f>
+        <v>437918</v>
+      </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -2093,7 +2129,7 @@
         <v>21</v>
       </c>
       <c r="C15" s="3">
-        <f t="shared" ref="C15:L15" si="2">+C13-C14</f>
+        <f t="shared" ref="C15:M15" si="2">+C13-C14</f>
         <v>442823</v>
       </c>
       <c r="D15" s="3">
@@ -2131,7 +2167,10 @@
       <c r="L15" s="3">
         <v>543871</v>
       </c>
-      <c r="M15" s="3"/>
+      <c r="M15" s="3">
+        <f t="shared" si="2"/>
+        <v>572037</v>
+      </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3">
@@ -2229,7 +2268,10 @@
       <c r="L16" s="3">
         <v>362555</v>
       </c>
-      <c r="M16" s="3"/>
+      <c r="M16" s="3">
+        <f>1090895-SUM(K16:L16)</f>
+        <v>366285</v>
+      </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -2316,7 +2358,10 @@
       <c r="L17" s="3">
         <v>9940</v>
       </c>
-      <c r="M17" s="3"/>
+      <c r="M17" s="3">
+        <f>24330-SUM(K17:L17)</f>
+        <v>9030</v>
+      </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -2403,7 +2448,10 @@
       <c r="L18" s="3">
         <v>1801</v>
       </c>
-      <c r="M18" s="3"/>
+      <c r="M18" s="3">
+        <f>3720-SUM(K18:L18)</f>
+        <v>889</v>
+      </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -2490,7 +2538,10 @@
       <c r="L19" s="3">
         <v>297</v>
       </c>
-      <c r="M19" s="3"/>
+      <c r="M19" s="3">
+        <f>1065-SUM(K19:L19)</f>
+        <v>-169</v>
+      </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -2544,7 +2595,7 @@
         <v>26</v>
       </c>
       <c r="C20" s="3">
-        <f t="shared" ref="C20:L20" si="4">+C15-C16+C17-C18+C19</f>
+        <f t="shared" ref="C20:M20" si="4">+C15-C16+C17-C18+C19</f>
         <v>146688</v>
       </c>
       <c r="D20" s="3">
@@ -2582,7 +2633,10 @@
       <c r="L20" s="3">
         <v>189752</v>
       </c>
-      <c r="M20" s="3"/>
+      <c r="M20" s="3">
+        <f t="shared" si="4"/>
+        <v>213724</v>
+      </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3">
@@ -2680,7 +2734,10 @@
       <c r="L21" s="3">
         <v>15832</v>
       </c>
-      <c r="M21" s="3"/>
+      <c r="M21" s="3">
+        <f>54500-SUM(K21:L21)</f>
+        <v>19281</v>
+      </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -2767,7 +2824,10 @@
       <c r="L22" s="3">
         <v>3447</v>
       </c>
-      <c r="M22" s="3"/>
+      <c r="M22" s="3">
+        <f>10652-SUM(K22:L22)</f>
+        <v>3571</v>
+      </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -2821,7 +2881,7 @@
         <v>29</v>
       </c>
       <c r="C23" s="3">
-        <f t="shared" ref="C23:L23" si="6">+C20+C21-C22</f>
+        <f t="shared" ref="C23:M23" si="6">+C20+C21-C22</f>
         <v>162473</v>
       </c>
       <c r="D23" s="3">
@@ -2859,7 +2919,10 @@
       <c r="L23" s="3">
         <v>202137</v>
       </c>
-      <c r="M23" s="3"/>
+      <c r="M23" s="3">
+        <f t="shared" si="6"/>
+        <v>229434</v>
+      </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3">
@@ -2956,7 +3019,10 @@
       <c r="L24" s="3">
         <v>58508</v>
       </c>
-      <c r="M24" s="3"/>
+      <c r="M24" s="3">
+        <f>198308-SUM(K24:L24)</f>
+        <v>71647</v>
+      </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -3010,7 +3076,7 @@
         <v>31</v>
       </c>
       <c r="C25" s="3">
-        <f t="shared" ref="C25:L25" si="8">+C23-C24</f>
+        <f t="shared" ref="C25:M25" si="8">+C23-C24</f>
         <v>114709</v>
       </c>
       <c r="D25" s="3">
@@ -3048,7 +3114,10 @@
       <c r="L25" s="3">
         <v>143629</v>
       </c>
-      <c r="M25" s="3"/>
+      <c r="M25" s="3">
+        <f t="shared" si="8"/>
+        <v>157787</v>
+      </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3">
@@ -3145,7 +3214,10 @@
       <c r="L26" s="3">
         <v>11785</v>
       </c>
-      <c r="M26" s="3"/>
+      <c r="M26" s="3">
+        <f>33851-SUM(K26:L26)</f>
+        <v>10999</v>
+      </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -3199,7 +3271,7 @@
         <v>33</v>
       </c>
       <c r="C27" s="3">
-        <f t="shared" ref="C27:L27" si="10">+C25-C26</f>
+        <f t="shared" ref="C27:M27" si="10">+C25-C26</f>
         <v>107804</v>
       </c>
       <c r="D27" s="3">
@@ -3237,7 +3309,10 @@
       <c r="L27" s="3">
         <v>131844</v>
       </c>
-      <c r="M27" s="3"/>
+      <c r="M27" s="3">
+        <f t="shared" si="10"/>
+        <v>146788</v>
+      </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3">
@@ -3397,7 +3472,10 @@
         <f t="shared" si="13"/>
         <v>429.69855129820922</v>
       </c>
-      <c r="M29" s="20"/>
+      <c r="M29" s="20">
+        <f t="shared" si="13"/>
+        <v>478.39374109713214</v>
+      </c>
       <c r="N29" s="20"/>
       <c r="O29" s="3"/>
       <c r="P29" s="20" t="e">
@@ -3493,7 +3571,9 @@
       <c r="L30" s="3">
         <v>306.82905399999999</v>
       </c>
-      <c r="M30" s="3"/>
+      <c r="M30" s="3">
+        <v>306.83511800000002</v>
+      </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
@@ -3619,7 +3699,7 @@
         <v>0.75231563552561598</v>
       </c>
       <c r="J32" s="21">
-        <f t="shared" ref="J32:L42" si="15">+J3/F3-1</f>
+        <f t="shared" ref="J32:M42" si="15">+J3/F3-1</f>
         <v>6.9010800780320736E-2</v>
       </c>
       <c r="K32" s="21">
@@ -3630,7 +3710,10 @@
         <f t="shared" si="15"/>
         <v>0.29365326352594434</v>
       </c>
-      <c r="M32" s="21"/>
+      <c r="M32" s="21">
+        <f t="shared" si="15"/>
+        <v>-9.599322192504911E-2</v>
+      </c>
       <c r="N32" s="21"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3707,7 +3790,10 @@
         <f t="shared" si="15"/>
         <v>8.121841368653171E-2</v>
       </c>
-      <c r="M33" s="21"/>
+      <c r="M33" s="21">
+        <f t="shared" si="15"/>
+        <v>0.1534811181167437</v>
+      </c>
       <c r="N33" s="21"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
@@ -3784,7 +3870,10 @@
         <f t="shared" si="15"/>
         <v>0.87066059993259182</v>
       </c>
-      <c r="M34" s="21"/>
+      <c r="M34" s="21">
+        <f t="shared" si="15"/>
+        <v>6.1653216567806313E-2</v>
+      </c>
       <c r="N34" s="21"/>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -3861,7 +3950,10 @@
         <f t="shared" si="15"/>
         <v>1.192982456140351</v>
       </c>
-      <c r="M35" s="21"/>
+      <c r="M35" s="21">
+        <f t="shared" si="15"/>
+        <v>-1.9407492396116388E-2</v>
+      </c>
       <c r="N35" s="21"/>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
@@ -3938,7 +4030,10 @@
         <f t="shared" si="15"/>
         <v>2.2368303126867159</v>
       </c>
-      <c r="M36" s="21"/>
+      <c r="M36" s="21">
+        <f t="shared" si="15"/>
+        <v>-0.10306730196545566</v>
+      </c>
       <c r="N36" s="21"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
@@ -4015,7 +4110,10 @@
         <f t="shared" si="15"/>
         <v>0.29365326352594434</v>
       </c>
-      <c r="M37" s="21"/>
+      <c r="M37" s="21">
+        <f t="shared" si="15"/>
+        <v>-9.599322192504911E-2</v>
+      </c>
       <c r="N37" s="21"/>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
@@ -4092,7 +4190,10 @@
         <f t="shared" si="15"/>
         <v>0.66793295972455513</v>
       </c>
-      <c r="M38" s="21"/>
+      <c r="M38" s="21">
+        <f t="shared" si="15"/>
+        <v>3.4020762453109921E-2</v>
+      </c>
       <c r="N38" s="21"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
@@ -4169,7 +4270,10 @@
         <f t="shared" si="15"/>
         <v>0.11811959863116983</v>
       </c>
-      <c r="M39" s="21"/>
+      <c r="M39" s="21">
+        <f t="shared" si="15"/>
+        <v>4.9527984862427488E-3</v>
+      </c>
       <c r="N39" s="21"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
@@ -4246,7 +4350,10 @@
         <f t="shared" si="15"/>
         <v>-0.1186092853106504</v>
       </c>
-      <c r="M40" s="21"/>
+      <c r="M40" s="21">
+        <f t="shared" si="15"/>
+        <v>7.8026244024511637E-2</v>
+      </c>
       <c r="N40" s="21"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
@@ -4323,7 +4430,10 @@
         <f t="shared" si="15"/>
         <v>0.11515151515151523</v>
       </c>
-      <c r="M41" s="21"/>
+      <c r="M41" s="21">
+        <f t="shared" si="15"/>
+        <v>0.55096418732782371</v>
+      </c>
       <c r="N41" s="21"/>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
@@ -4400,7 +4510,10 @@
         <f t="shared" si="15"/>
         <v>0.14801688480300701</v>
       </c>
-      <c r="M42" s="22"/>
+      <c r="M42" s="22">
+        <f t="shared" si="15"/>
+        <v>0.22195133755187468</v>
+      </c>
       <c r="N42" s="22"/>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
@@ -4486,10 +4599,13 @@
         <v>0.5523772920325567</v>
       </c>
       <c r="L43" s="21">
-        <f t="shared" ref="L43" si="19">+L15/L13</f>
+        <f t="shared" ref="L43:M43" si="19">+L15/L13</f>
         <v>0.52932411468035445</v>
       </c>
-      <c r="M43" s="21"/>
+      <c r="M43" s="21">
+        <f t="shared" si="19"/>
+        <v>0.56639850290359472</v>
+      </c>
       <c r="N43" s="21"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
@@ -4575,10 +4691,13 @@
         <v>0.20522113948498899</v>
       </c>
       <c r="L44" s="21">
-        <f t="shared" ref="L44" si="22">+L20/L13</f>
+        <f t="shared" ref="L44:M44" si="22">+L20/L13</f>
         <v>0.18467671453125212</v>
       </c>
-      <c r="M44" s="21"/>
+      <c r="M44" s="21">
+        <f t="shared" si="22"/>
+        <v>0.21161734928783957</v>
+      </c>
       <c r="N44" s="21"/>
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
@@ -4664,10 +4783,13 @@
         <v>0.30067323133393331</v>
       </c>
       <c r="L45" s="21">
-        <f t="shared" ref="L45" si="25">+L24/L23</f>
+        <f t="shared" ref="L45:M45" si="25">+L24/L23</f>
         <v>0.28944725606890376</v>
       </c>
-      <c r="M45" s="21"/>
+      <c r="M45" s="21">
+        <f t="shared" si="25"/>
+        <v>0.31227716903336034</v>
+      </c>
       <c r="N45" s="21"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3"/>
